--- a/daily_matches/job_matches_2026-09-17.xlsx
+++ b/daily_matches/job_matches_2026-09-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II - Homes.com - Arlington, VA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DigiCert</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Gemini, Copilot, Prompt Engineering, S3, BigQuery, Data Lake, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99b6f6fafc93a2b2</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e22789e6fc7a92</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Backend Software Engineer III - Python/JAVA</t>
+          <t>Sr Software Engineer II - Enterprise Architecture</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>24.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Glue, Athena, Kubernetes, CI/CD, Terraform, Git, Snowflake, PySpark</t>
+          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e860daaeaca47c2</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b0b7c55fd4efa0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer (Temporal &amp; Apache Kafka required)</t>
+          <t>AI and Data Solution Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Glue, Redshift, BigQuery, CI/CD, Snowflake, Databricks, BigQuery, Redshift</t>
+          <t>Generative AI, RAG, FAISS, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aecdd03e33db9d0</t>
+          <t>https://www.indeed.com/viewjob?jk=1d9d060e7277ff6e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>AI and Data Solution Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>22.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Azure ML, MLflow, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake</t>
+          <t>Generative AI, RAG, FAISS, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc9434d3c199f7af</t>
+          <t>https://www.indeed.com/viewjob?jk=9bb20dd369056bd0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Corporate GenAI</t>
+          <t>Sr. SW AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, Prompt Engineering, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Copilot, Pinecone, Prompt Engineering, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98c6a0f35165b0f3</t>
+          <t>https://www.indeed.com/viewjob?jk=69e861b829f3c992</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>AI Engineer Consultant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
+          <t>AI Engineer, RAG, Azure ML, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=913f326777591b8d</t>
+          <t>https://www.indeed.com/viewjob?jk=391da6433d5d0e7e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI full stack Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>valency systems</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Copilot, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Kafka, PostgreSQL, MySQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10c6b6037cda414d</t>
+          <t>https://www.indeed.com/viewjob?jk=7faadf86698e0022</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Development Engineer (Machine Learning)</t>
+          <t>Data Scientist II, Client Analysis</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fortinet</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Hugging Face, PyTorch, XGBoost, LightGBM, Docker, Kubernetes, AKS, Git</t>
+          <t>Data Scientist, RAG, S3, Redshift, Git, Snowflake, Databricks, Redshift, PySpark, Tableau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1306c5da58fba883</t>
+          <t>https://www.indeed.com/viewjob?jk=517cb357cd124c78</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gen AI Engineer-4</t>
+          <t>Data Scientist II, Client Analysis</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Python, SQL</t>
+          <t>Data Scientist, RAG, S3, Redshift, Git, Snowflake, Databricks, Redshift, PySpark, Tableau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6e307d4bafa0250</t>
+          <t>https://www.indeed.com/viewjob?jk=2e210c5f4e92ef2c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Data Scientist II, Client Analysis</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL, Python, SQL</t>
+          <t>Data Scientist, RAG, S3, Redshift, Git, Snowflake, Databricks, Redshift, PySpark, Tableau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41480985be8d777</t>
+          <t>https://www.indeed.com/viewjob?jk=2c570349a74757f0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist II, Client Analysis</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, Kafka, MySQL, SQL, R, Java</t>
+          <t>Data Scientist, RAG, S3, Redshift, Git, Snowflake, Databricks, Redshift, PySpark, Tableau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a37c4760006d71ef</t>
+          <t>https://www.indeed.com/viewjob?jk=8f2e1fdb2dae1f8a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Precision Oncology</t>
+          <t>Data Scientist II, Client Analysis</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Moffitt Cancer Center</t>
+          <t>Socure</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Hugging Face, PyTorch, CI/CD, Git, Python, R</t>
+          <t>Data Scientist, RAG, S3, Redshift, Git, Snowflake, Databricks, Redshift, PySpark, Tableau</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e29adf89799044b</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2d9f8318867372</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI/ML Engineer Precision Oncology</t>
+          <t>Associate, AWS Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Moffitt Cancer Center</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Hugging Face, PyTorch, CI/CD, Git, Python, R</t>
+          <t>RAG, S3, Glue, Athena, Redshift, CI/CD, Terraform, Redshift, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00cd66c1a5e5e12b</t>
+          <t>https://www.indeed.com/viewjob?jk=dceec67b928233eb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Engineering Intern</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vusion</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, OpenCV, Docker, Kubernetes, CI/CD, Git, Python, SQL</t>
+          <t>RAG, Copilot, Synapse, CI/CD, Git, Snowflake, Databricks, PySpark, Power BI, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=541bfd09c4a69091</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfb266cf22e5317</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Agent Developer</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Corpay</t>
+          <t>Xenith Solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Git, Power BI, Python, SQL</t>
+          <t>Data Scientist, RAG, FastAPI, Docker, Kubernetes, Git, Kafka, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96d3a70f400f2313</t>
+          <t>https://www.indeed.com/viewjob?jk=0e8c68977bffcc0a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Agent Developer</t>
+          <t>Tech Consultant - Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Corpay</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,77 +1011,77 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Git, Power BI, Python, SQL</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32cd963d77c883c9</t>
+          <t>https://www.indeed.com/viewjob?jk=7b83ab91a7807af3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Agent Developer</t>
+          <t>Full-Stack Software Engineer (ReactJS / Node.js)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Corpay</t>
+          <t>Marketron</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Auburn, AL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Git, Power BI, Python, SQL</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c4fd36ba12e3c81</t>
+          <t>https://www.indeed.com/viewjob?jk=e62ab710ef362d6b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Agent Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Corpay</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New Castle, DE, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Git, Power BI, Python, SQL</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a48e4368fb408127</t>
+          <t>https://www.indeed.com/viewjob?jk=cffabdfd8430d2e8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gen AI Engineer-3</t>
+          <t>Junior Site Relaibilty Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,29 +1116,29 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, PostgreSQL, Python, SQL, R, Java</t>
+          <t>Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=814280d6c27316f6</t>
+          <t>https://www.indeed.com/viewjob?jk=ba67d3aa515dfd62</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Data Science - AI Document Understanding, Co-op</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ancestry</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, Gemini, Hugging Face, NLTK, S3, EC2, Python, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0632f545cc6501af</t>
+          <t>https://www.indeed.com/viewjob?jk=2c94b55544ee6682</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Esker</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Middleton, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Kafka, PostgreSQL, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=412a59dba3fa1861</t>
+          <t>https://www.indeed.com/viewjob?jk=b1bb9597fe2505bc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=576bfac62cf9aa48</t>
+          <t>https://www.indeed.com/viewjob?jk=6fd203a4dd577d3c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=289a1c2f73837ce8</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ab9a2013dcb88a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Senior QA Automation Engineer (CirrusMD)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Quantum Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Gemini, Copilot, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8f3e421b328a92</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e97cf59de88998</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Alembic Pharmaceuticals Ltd</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dunwoody, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Data Scientist, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed0857e69b90e470</t>
+          <t>https://www.indeed.com/viewjob?jk=75b83ee2f5d53bc7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Distributed Systems Engineer, Payment System Redundancy</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, R, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b2f3cbc16bed28</t>
+          <t>https://www.indeed.com/viewjob?jk=bc48497c3845cf99</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Zelis Healthcare</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9878b5a9872dda53</t>
+          <t>https://www.indeed.com/viewjob?jk=675ef5f637eb1f31</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Senior Software Engineer, Cloud Services</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Docker, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57261d86d11a118</t>
+          <t>https://www.indeed.com/viewjob?jk=2d73cc173ac49c0f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>AI Engineer, Industrial Systems Data Platform (ISDP)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>AI Engineer, RAG, BigQuery, Dataflow, CI/CD, Terraform, BigQuery, Python, R, Java</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9487aa9f28779178</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfa369c43ecbae0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>AI Data &amp; Security Governance Engineer (MAD-BS-OR)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Pinecone, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=942bba2df6f37718</t>
+          <t>https://www.indeed.com/viewjob?jk=09a919fafd772071</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Snowflake, Kafka, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7739b5047d1984a1</t>
+          <t>https://www.indeed.com/viewjob?jk=12125842d5128534</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>2027 PhD AI Model Optimization &amp; Software Engineer Intern/Co-op</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, CI/CD, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f6408c24edc3c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=3c4da008fe155468</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>2027 PhD AI Model Optimization &amp; Software Engineer Intern/Co-op</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, CI/CD, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c700c3c53a5724e2</t>
+          <t>https://www.indeed.com/viewjob?jk=39ed1d4be0b63022</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Product Owner (AI)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Wesco</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jersey Village, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8683769999f004</t>
+          <t>https://www.indeed.com/viewjob?jk=9747f7e5b52dee4a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>AI Data &amp; Security Governance Engineer (MAD-BS-OR)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Pinecone, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4952000efb0f0a2b</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4c21a1bba06dc6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a98f4127e49289</t>
+          <t>https://www.indeed.com/viewjob?jk=b1723adfb624e5ed</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Senior Software Engineer – AI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>National Fire Protection Association</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Generative AI, RAG, Docker, CI/CD, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df47ed92ea817c93</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc65cbf5328fce4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Associate AI Software Engineer-2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>ChenMed</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Pinecone, FastAPI, Docker, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b953778f4b275a78</t>
+          <t>https://www.indeed.com/viewjob?jk=e18bbeac2433ded0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>BI Analyst</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Generative AI, RAG, Snowflake, Databricks, Power BI, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131dcd2aa504d18c</t>
+          <t>https://www.indeed.com/viewjob?jk=866d36b170e14175</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Shamrock Trading Corporation</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Redshift, Git, Databricks, Redshift, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7c5f8aef707359f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7551ad0611d9a66</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Copilot, S3, Docker, CI/CD, Jenkins, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca496c739be4f1f3</t>
+          <t>https://www.indeed.com/viewjob?jk=8a82852b0c2239ec</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Agentic Data Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>CI/CD, Git, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51e922690013fc29</t>
+          <t>https://www.indeed.com/viewjob?jk=1c17eb0b6e6f6925</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Sr Security Engineer - DDOS and Bot Defense</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, Kafka, R, Java, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,102 +1966,102 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=006eb40f82629c98</t>
+          <t>https://www.indeed.com/viewjob?jk=dc8701e67fba0550</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Full-Stack AI Application Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Ontrac Solutions</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Machine Learning Engineer, RAG, Gemini, FastAPI, Docker, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c527692db6415314</t>
+          <t>https://www.indeed.com/viewjob?jk=4213b637181e99af</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Full-Stack AI Application Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Ontrac Solutions</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Machine Learning Engineer, RAG, Gemini, FastAPI, Docker, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86fd9eb377dc39e1</t>
+          <t>https://www.indeed.com/viewjob?jk=270caa831124e4f7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Investment Systems Senior Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Colorado Public Employees' Retirement Association</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Athena, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0d6586c29d4c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=2b86fa1e4a4e1bf0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Machine Learning Engineer, PyTorch, XGBoost, LightGBM, Python, SQL, R, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f33aff7373abbee</t>
+          <t>https://www.indeed.com/viewjob?jk=6662915f7dec1b29</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e34a57723c42ab</t>
+          <t>https://www.indeed.com/viewjob?jk=89ceaefe787905ee</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aed53912598d4355</t>
+          <t>https://www.indeed.com/viewjob?jk=f39ad18dc165ab93</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fc1b5ad963f16e5</t>
+          <t>https://www.indeed.com/viewjob?jk=d554ce2b6f661051</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior DevOps Platform Engineer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=460c455a83fba71c</t>
+          <t>https://www.indeed.com/viewjob?jk=7690cb4a348ffa33</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Based in India</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Credibly</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, FastAPI, Docker, CI/CD, Terraform, MySQL, Python, SQL</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc86ee3cbc668eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=9858b339b4aa6880</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed Engineer// Senior AI/ML Engineer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bravent LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, AKS, CI/CD, Git, Snowflake, Databricks, R</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca81d5a91635f6a</t>
+          <t>https://www.indeed.com/viewjob?jk=5e9b079a14cc7ae1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Context and Semantics (AI)</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Pinecone, Data Lake, Python, SQL, R, Java</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a03195a7efe601b</t>
+          <t>https://www.indeed.com/viewjob?jk=cd1ea8194560aceb</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer - Context and Semantics (AI)</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Pinecone, CI/CD, Python, SQL, R, Java</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc4e2ec7beec70d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f109411bc0ebf5eb</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Technology - Enterprise Data Architect</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Aritzia</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Synapse, Git, Snowflake, Databricks, BigQuery, Redshift, Kafka, R</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72f1d8c4f42885d</t>
+          <t>https://www.indeed.com/viewjob?jk=b0aaf12f0984ec7f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, MLflow, Git, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f285c23f3470241</t>
+          <t>https://www.indeed.com/viewjob?jk=77369e588ad2760f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tillster</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, Cortex, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c43aaeceb285263</t>
+          <t>https://www.indeed.com/viewjob?jk=a45ac9878b686f15</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tillster</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, Cortex, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e81d173e43e8b712</t>
+          <t>https://www.indeed.com/viewjob?jk=81f486bac1b643d0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee14dc761cbf374d</t>
+          <t>https://www.indeed.com/viewjob?jk=3df7d7c6071ac7cc</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior .NET Solutions Developer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=707100e1f0be29ca</t>
+          <t>https://www.indeed.com/viewjob?jk=1e87d3ca59819bb6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full-stack Java and React Software Engineer III</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76dab07201ea443a</t>
+          <t>https://www.indeed.com/viewjob?jk=1489754db2a7bcf1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>alliantgroup</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, AKS, Git, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=246b7174dd382b16</t>
+          <t>https://www.indeed.com/viewjob?jk=271f966e1bfaef86</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - CorePointAI</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f90deb2a1278705</t>
+          <t>https://www.indeed.com/viewjob?jk=02dd398597776f87</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - CorePointAI</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a864fcd2a9573f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=9cdc9834e4c6e096</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - CorePointAI</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524be37cacd3bd8f</t>
+          <t>https://www.indeed.com/viewjob?jk=135a3a9eec426eb6</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - CorePointAI</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,19 +2806,19 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bae2e9dd177ca28</t>
+          <t>https://www.indeed.com/viewjob?jk=1c2e663592f54fbe</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - CorePointAI</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2827,11 +2827,11 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acdc597e0019f847</t>
+          <t>https://www.indeed.com/viewjob?jk=c152232cc2b36d07</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - CorePointAI</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3c80738241f8654</t>
+          <t>https://www.indeed.com/viewjob?jk=968b63dccf02e798</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - CorePointAI</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7614aedbe0a38003</t>
+          <t>https://www.indeed.com/viewjob?jk=5393b13125591681</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer - (Hybrid - Herndon, VA)</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb9bdf40642b887</t>
+          <t>https://www.indeed.com/viewjob?jk=fabb0d3e5c32582e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer II</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bureau Veritas</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Copilot, FastAPI, Docker, Kubernetes, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6520452dabe3fb04</t>
+          <t>https://www.indeed.com/viewjob?jk=c6cf958bdd2c5118</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer II</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Git, Python, R, Scala, Bayesian</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f57caeb6f6414d9e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e8cab24c2faf6a4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Kubernetes, AKS, CI/CD, MongoDB, Python, R, Optimization</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3894cbd54c23a706</t>
+          <t>https://www.indeed.com/viewjob?jk=4bdd1c5b48957150</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Databricks, PySpark, Python, SQL, R, Hypothesis Testing</t>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,567 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea44209ce594bcf</t>
+          <t>https://www.indeed.com/viewjob?jk=687c6db1f2f109c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09234f116601ff13</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8e3e56c47dde7ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee03048c96e565c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=788702fbd09bf873</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Fresno, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e27584e825d85b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f183a4c9d68d19fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9780c1dad00031ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ae886e06ca4f9b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb43159a3ceebd0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0a6bb4f09a88d7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=268e377da8df52a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73a5b24648de37a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=872ddf80a88102a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8412a7d61cebbefd</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15a4f3bc5168e489</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=085fa3fc32b6ad1f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-17.xlsx
+++ b/daily_matches/job_matches_2026-09-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,130 +468,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Managing Consultant, Databricks Engineer/Architect - Birmingham, AL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>East West Bank</t>
+          <t>Thought Logic Consulting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Mistral, Prompt Engineering, Azure ML</t>
+          <t>Copilot, Redshift, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14edeae1a2c79e5c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb9b402f0c526caf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Architect - Azure Data &amp; AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>East West Bank</t>
+          <t>Coretek Services</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Mistral, Prompt Engineering, Azure ML</t>
+          <t>AI Engineer, RAG, Synapse, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Databricks, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071a150cb3b8b351</t>
+          <t>https://www.indeed.com/viewjob?jk=9bbe65f2b6e82102</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>East West Bank</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Mistral, Prompt Engineering, Azure ML</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a255c79df459cd3</t>
+          <t>https://www.indeed.com/viewjob?jk=45d9772de89f1c0a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, Keras, NLTK, AWS SageMaker, Docker, Kubernetes, CI/CD, Git</t>
+          <t>Copilot, S3, Glue, Redshift, Git, Redshift, MongoDB, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c85f07df0a6c0e82</t>
+          <t>https://www.indeed.com/viewjob?jk=978f9a7dd296c785</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Generative AI Scientist II - (Model Risk)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>ECPI University</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Mistral, TensorFlow, PyTorch, Keras, NLTK</t>
+          <t>RAG, Copilot, Cortex, CI/CD, GitHub Actions, Git, Snowflake, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e829816d12ee51</t>
+          <t>https://www.indeed.com/viewjob?jk=48f9cd78305a0219</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>ECPI University</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Copilot, EC2, Docker, CI/CD, Git, Kafka, PostgreSQL, MongoDB, NoSQL, Python</t>
+          <t>RAG, Cortex, Dataflow, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2779eda0004077f</t>
+          <t>https://www.indeed.com/viewjob?jk=13dc5ea105826d16</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Technical Business Analyst</t>
+          <t>AI Engineer – Software Development Tools</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, Snowflake, Databricks, Tableau, Power BI, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,102 +706,102 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c7dea3197e41589</t>
+          <t>https://www.indeed.com/viewjob?jk=4a4a7028935e6c28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Engineer – Software Development Tools</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aramark</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd261c364b06e86</t>
+          <t>https://www.indeed.com/viewjob?jk=055ce6dc6a7601ec</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Machine Learning Engineer, Vector Bidding Science</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>All IT Solutions</t>
+          <t>Unity Technologies</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Jenkins, Git, Python</t>
+          <t>Machine Learning Engineer, RAG, Copilot, PyTorch, BigQuery, Git, BigQuery, Python, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fdd34dbd5588c0b</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd26d24466a654b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer, New College Grad, Bellevue - 2027</t>
+          <t>Senior Machine Learning Engineer, Vector Bidding Science</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Unity Technologies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, Copilot, Git, MySQL, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>Machine Learning Engineer, RAG, Copilot, PyTorch, BigQuery, Git, BigQuery, Python, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=448c86d1abca3003</t>
+          <t>https://www.indeed.com/viewjob?jk=6aa2a3eb401f5c2c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer - SRE</t>
+          <t>Senior Data Scientist - Actuarial</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>DOWC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Snowflake, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42584a3d1ce5783d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1e6ee6df4a8453</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - AI Platform</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Oldcastle APG</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -867,46 +867,46 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Cortex, Snowflake, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c378a5dbeec0c24c</t>
+          <t>https://www.indeed.com/viewjob?jk=4e6f322e6c8492e6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Automation Engineer (UI/API)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Vuedata</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, S3, Git, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc8f98df2baf90f</t>
+          <t>https://www.indeed.com/viewjob?jk=405db37782698de8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Automation Engineer (UI/API)</t>
+          <t>IT Data Engineer-Level 3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, Data Lake, Dataflow, CI/CD, Terraform, PySpark, Hadoop, Power BI, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70cd80ce62300845</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0d8372bb750a76</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Automation Engineer (UI/API)</t>
+          <t>Software Engineer, New College Grad - 2027 Foster City, CA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+          <t>Generative AI, Copilot, Git, MySQL, Power BI, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4a65a0fcd7eaa2</t>
+          <t>https://www.indeed.com/viewjob?jk=63ed8b1b41b41f1b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Automation Engineer (UI/API)</t>
+          <t>Software Engineer, New College Grad - 2027, Austin, TX</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+          <t>Generative AI, Copilot, Git, MySQL, Power BI, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef50bf754cb562dd</t>
+          <t>https://www.indeed.com/viewjob?jk=cb489a4d7d4a0f29</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Automation Engineer (UI/API)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Univerze LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Sudbury, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e56db417fdabcef</t>
+          <t>https://www.indeed.com/viewjob?jk=170890bd4e26aa67</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Automation Engineer (UI/API)</t>
+          <t>Life Sciences AI Intelligence Extern / Intern</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Harrison Hayes, LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+          <t>Data Scientist, Generative AI, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63cf03e83c9963c7</t>
+          <t>https://www.indeed.com/viewjob?jk=140f98192531d352</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Machine Learning Engineer, Advertiser Growth</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>All IT Solutions</t>
+          <t>Unity Technologies</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Data Lake, CI/CD, Git, MongoDB, Python, SQL, R</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Kafka, R, Java, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63e200f762907a6d</t>
+          <t>https://www.indeed.com/viewjob?jk=5b144dcfc101df5d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Information Technology - DevOps Engineer (Cloud Engineer)</t>
+          <t>Senior Machine Learning Engineer, Advertiser Growth</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>All IT Solutions</t>
+          <t>Unity Technologies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,157 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Kafka, R, Java, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a73e24cf8ec17564</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, Advertiser Growth</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Unity Technologies</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Kafka, R, Java, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db39e4d89931d3da</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Software Engineer, Intern - 2027 Ashburn, VA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Generative AI, Copilot, Docker, Kubernetes, Git, Kafka, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=884f37c91f722e71</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Software Engineer, Intern, Highlands Ranch, CO - 2027</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Highlands Ranch, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Generative AI, Copilot, Docker, Kubernetes, Git, Kafka, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b5d9837ce77e4da</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>O'Fallon, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c9424b6e5898666</t>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9f019727a4e040f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-17.xlsx
+++ b/daily_matches/job_matches_2026-09-17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Managing Consultant, Databricks Engineer/Architect - Birmingham, AL</t>
+          <t>A/AI Machine Learning Engineering Stf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Thought Logic Consulting</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Copilot, Redshift, BigQuery, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, S3, Redshift, BigQuery, Data Lake, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9b402f0c526caf</t>
+          <t>https://www.indeed.com/viewjob?jk=601d6d86d645df17</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Architect - Azure Data &amp; AI</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Coretek Services</t>
+          <t>Gen Digital Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Synapse, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Databricks, Kafka</t>
+          <t>LangChain, RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bbe65f2b6e82102</t>
+          <t>https://www.indeed.com/viewjob?jk=95fd25995bfa0bb4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior AWS Full Stack Engineer local only</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>VaaridaTech</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
+          <t>Generative AI, RAG, S3, Glue, Athena, Redshift, Data Lake, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45d9772de89f1c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=99e004b7468d7a58</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Snowflake Platform Admin + Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Copilot, S3, Glue, Redshift, Git, Redshift, MongoDB, Tableau, Power BI, Python</t>
+          <t>Generative AI, RAG, Gemini, S3, Glue, Apache Airflow, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=978f9a7dd296c785</t>
+          <t>https://www.indeed.com/viewjob?jk=6bab71f3dab957b3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ECPI University</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Cortex, CI/CD, GitHub Actions, Git, Snowflake, Tableau, Power BI, Python</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Keras, Snowflake, Databricks, Hadoop, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f9cd78305a0219</t>
+          <t>https://www.indeed.com/viewjob?jk=07271acb0c0e4124</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Contact Center Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ECPI University</t>
+          <t>Presidio</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Cortex, Dataflow, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, SQL</t>
+          <t>Generative AI, RAG, Copilot, S3, Data Lake, Kinesis, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13dc5ea105826d16</t>
+          <t>https://www.indeed.com/viewjob?jk=cf9a0e1dc867d738</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Engineer – Software Development Tools</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Mediacom Communications Corporation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Blooming Grove, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, Python, R, Java</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a4a7028935e6c28</t>
+          <t>https://www.indeed.com/viewjob?jk=e9ae15ce1f6d277d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Engineer – Software Development Tools</t>
+          <t>Data Architect – FDE | Hartford, CT / Minneapolis, MN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Inabia Software &amp; Consulting Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, Python, R, Java</t>
+          <t>RAG, Synapse, Kubernetes, AKS, CI/CD, Terraform, Databricks, PySpark, Kafka, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=055ce6dc6a7601ec</t>
+          <t>https://www.indeed.com/viewjob?jk=a6b512ada906a24d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Vector Bidding Science</t>
+          <t>DoW SkillBridge Fellowship - Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Unity Technologies</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Pensacola, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Copilot, PyTorch, BigQuery, Git, BigQuery, Python, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, MLflow, CI/CD, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd26d24466a654b</t>
+          <t>https://www.indeed.com/viewjob?jk=55bc5e594868950c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Vector Bidding Science</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Unity Technologies</t>
+          <t>ICBD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Copilot, PyTorch, BigQuery, Git, BigQuery, Python, R, Scala</t>
+          <t>Generative AI, Prompt Engineering, FastAPI, CI/CD, Git, Databricks, PySpark, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa2a3eb401f5c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=6c0d34c2d7c8f353</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Actuarial</t>
+          <t>Associate AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DOWC</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Snowflake, Power BI, Python, SQL, R, Scala</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, Docker, Kubernetes, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1e6ee6df4a8453</t>
+          <t>https://www.indeed.com/viewjob?jk=7d761a996e119319</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Oldcastle APG</t>
+          <t>CodeCombat</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Cortex, Snowflake, Tableau, Python, SQL, R</t>
+          <t>Data Scientist, RAG, S3, Redshift, Data Lake, Redshift, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e6f322e6c8492e6</t>
+          <t>https://www.indeed.com/viewjob?jk=96af3bdac24317bb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Emerging Risk Strategic Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vuedata</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, S3, Git, Python</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=405db37782698de8</t>
+          <t>https://www.indeed.com/viewjob?jk=4bb419923f9889d0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IT Data Engineer-Level 3</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Dataflow, CI/CD, Terraform, PySpark, Hadoop, Power BI, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Gemini, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0d8372bb750a76</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff62d532162ce32</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer, New College Grad - 2027 Foster City, CA</t>
+          <t>AI Developer Mathematics-Focused (Math + Computer Science)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Roartech Inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, Copilot, Git, MySQL, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>RAG, LLaMA, PyTorch, FastAPI, Docker, Git, MongoDB, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63ed8b1b41b41f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=fa6bb4f4f9da3365</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer, New College Grad - 2027, Austin, TX</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Interra Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, Copilot, Git, MySQL, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb489a4d7d4a0f29</t>
+          <t>https://www.indeed.com/viewjob?jk=36507dc432cb2270</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer Con II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Univerze LLC</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sudbury, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, CI/CD, Snowflake, Databricks, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,19 +1056,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=170890bd4e26aa67</t>
+          <t>https://www.indeed.com/viewjob?jk=d4db0b036f71a516</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Life Sciences AI Intelligence Extern / Intern</t>
+          <t>Applied Machine Learning Engineer Senior Consultant II (Software Engineering Focus)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Harrison Hayes, LLC</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1077,11 +1077,11 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, MongoDB, Python, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=140f98192531d352</t>
+          <t>https://www.indeed.com/viewjob?jk=f1ad4011aca5d4a8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Advertiser Growth</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Unity Technologies</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Kafka, R, Java, Scala, Optimization, A/B Testing</t>
+          <t>RAG, Kubernetes, CI/CD, Databricks, Kafka, Hadoop, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b144dcfc101df5d</t>
+          <t>https://www.indeed.com/viewjob?jk=228fcb0437db4c81</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Advertiser Growth</t>
+          <t>Senior Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Unity Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Kafka, R, Java, Scala, Optimization, A/B Testing</t>
+          <t>Generative AI, RAG, Gemini, Apache Airflow, CI/CD, Git, Databricks, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a73e24cf8ec17564</t>
+          <t>https://www.indeed.com/viewjob?jk=d445976e1497f7fc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Advertiser Growth</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Unity Technologies</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Kafka, R, Java, Scala, Optimization, A/B Testing</t>
+          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db39e4d89931d3da</t>
+          <t>https://www.indeed.com/viewjob?jk=27203176a444972f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern - 2027 Ashburn, VA</t>
+          <t>Site Reliability Engineer 2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, Copilot, Docker, Kubernetes, Git, Kafka, Python, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=884f37c91f722e71</t>
+          <t>https://www.indeed.com/viewjob?jk=fd4b4423de389261</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern, Highlands Ranch, CO - 2027</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Highlands Ranch, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Generative AI, Copilot, Docker, Kubernetes, Git, Kafka, Python, R, Java</t>
+          <t>RAG, CI/CD, Git, Kafka, Cassandra, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,42 +1266,1792 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5d9837ce77e4da</t>
+          <t>https://www.indeed.com/viewjob?jk=94865fb914de5c24</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Research Engineer, Institute for Software Integrated Systems</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Vanderbilt University</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>FastAPI, Docker, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL, R, Julia</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d00695e9ba25e7f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Analytics Engineer III</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Shaw Industries</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Dalton, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Dataflow, CI/CD, Git, Databricks, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84b8ba5b4701ac07</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data Scientist 100% Remote – Must be US Citizen due to Public Trust Clearance</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Cypress Consulting</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, Databricks, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f4859d814e3f8fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Full Stack Solutions Developer – Java</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5aa577a3ce581c79</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Machine Learning Platform</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, S3, EC2, Kubernetes, CI/CD, Dask, Python, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad39fff1284a19e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AWS DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Sioux Falls, SD, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, GitHub Actions, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12833ce59c1ff185</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Hardware Data Analyst</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Aperia Technologies</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, Redshift, Kinesis, Redshift, Tableau, Quicksight, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9da704742d2ca4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Hardware Data Analyst</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Aperia Technologies</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, Redshift, Kinesis, Redshift, Tableau, Quicksight, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=395c7bcabcffea9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Year-Round Intern - AI Research &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Options Clearing Corporation</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49319d6923ff84c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Junior / Mid-Level AI &amp; Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Docker, CI/CD, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc53f2cac7fd0eec</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Applied AI ML Senior Associate -AI Agents &amp; Agentic Systems</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f3b221c58dab048</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Sr Marketing Data Scientist</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ATHENE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>West Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Copilot, S3, Athena, Tableau, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce21a2248af0f5a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Accelerate - IT Engineering Intern Summer 2027</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Avis Budget Group</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f387e1166f678ff7</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Accelerate - IT Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Avis Budget Group</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33fd032937113a12</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Abacus</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, Copilot, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb29ca22c38298f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SCUBI - Software Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Docker, AKS, Git, MongoDB, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12e1835f67d2cb9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>4572 Software Development Engineer III</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Innovaccer</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Athena, FastAPI, Docker, Kubernetes, CI/CD, MongoDB, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0dbd91cc3292ce05</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer, Fullstack</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>VoltaGrid</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24b02a3e8026450a</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>QUADRIC PTY LTD</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Burlingame, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88367302496f71f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Janus Henderson Investors</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Docker, CI/CD, Terraform, Snowflake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6877afcf6e3eae4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>LLM Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>University of North Carolina at Chapel Hill</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Chapel Hill, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Docker, Kubernetes, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=873819ff30096388</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Digital Experience</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Everpure</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, AKS, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a87fc323fb9f4ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Agentic AI Engineer II - Global Infrastructure</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, Prompt Engineering, Git, Hadoop, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24b0a0c9398646b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Python Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f81d7b9839378748</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Software Engineer III - ML Model Delivery</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, Docker, Kubernetes, Terraform, Databricks, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3dbcf1eaec6697a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer III - AWS, Java and Kubernetes</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fff9ab8e0bdf65bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SDC Camunda Workflow Automation Engineer---Analyst---Raleigh, NC or Dallas, TX</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5234b4d2469f439f</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>AI-Enabled Full-Stack Software Engineering Intern</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Lennox International</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Copilot, Prompt Engineering, AKS, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f60ab49a5d075a25</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Python/AWS/AI</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4709e806fcfa541</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>AI &amp; Data Science Intern</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Ericsson</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Tableau, Power BI, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68c00716cf82fa14</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Azure Devops Architect</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, AKS, CI/CD, GitHub Actions, Terraform, Git, SQL, R</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e71a450aa73d307a</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Kubernetes, CI/CD, Git, Kafka, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=666010919d5ec664</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Developer/Engineer - L2</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>BigQuery, Docker, Kubernetes, CI/CD, Git, BigQuery, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2d5dfd97b3ec7c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Network Engineer, Product Software</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Equinix</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
         <v>10</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, Git, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f019727a4e040f</t>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f6d041610320686</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Software Engineer 3</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5d12f51c7fd2e3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Software Engineer- GovCloud</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Copilot, Prompt Engineering, Docker, Kubernetes, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=10bd24e705855716</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Software Engineer, DNS &amp; Cloud Infrastructure</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=998b59d45987a604</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior, Specialist SE</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c030f758b6a51a84</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>QA Automation Engineer-JavaScript/Cypress with ML/AI - Only local to NY/NJ/CT</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Sunsoft Services Inc</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Docker, CI/CD, Jenkins, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34b56ba05d00f22c</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer II</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>YUM! Brands, Inc.</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>S3, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2830b10b4939c5e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Azure Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31b1476596d9d7bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Java AWS Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, CI/CD, Terraform, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5651b7ee9138b28f</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Possible Finance</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Data Scientist, XGBoost, MLflow, Databricks, PySpark, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8db13b459057bcfd</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Data Scientist, Pharmacy (Part D Stars)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Alignment Health</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Orange, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Data Scientist, CI/CD, Git, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b946979afc5a348c</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>A/AI Machine Learning Engineering Senior</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Lockheed Martin</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, LangChain, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a64a4fe5838110dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>A/AI Machine Learning Engineering Senior</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Lockheed Martin</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, LangChain, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f55594b0c6da39a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>A/AI Machine Learning Engineering Senior</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Lockheed Martin</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, LangChain, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=644db64d6018ee49</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>AI Machine Learning Engineering Senior</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Lockheed Martin</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, LangChain, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ef1edb3a0a062e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Software Engineer, Intern, Bellevue - 2027</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Generative AI, Copilot, Docker, Kubernetes, Git, Kafka, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89c0d8d7b8be7b0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>JAVA Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, Git, Kafka, R, Java</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=077a14efca7a6d1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Roblox Database</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Roblox</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94ed0dbeeb2f8d10</t>
         </is>
       </c>
     </row>
